--- a/Multitask-stats.xlsx
+++ b/Multitask-stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bitininkas/projects/3body-simulator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yayax\projects\3body-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E37BC4-2A63-F548-A097-780BE3CFE3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BCA2F9-993D-416B-BAD2-AECCEBB78B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16560" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -120,7 +120,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -505,6 +505,36 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1427,9 +1457,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1467,7 +1497,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -1573,7 +1603,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1744,14 +1774,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDD5B6A-F05D-A248-86D7-3519E8114CE9}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1762,7 +1792,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>0</v>
@@ -1777,7 +1807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1787,8 +1817,11 @@
       <c r="C3">
         <v>25</v>
       </c>
+      <c r="D3">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1798,8 +1831,11 @@
       <c r="C4">
         <v>13</v>
       </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1809,8 +1845,11 @@
       <c r="C5">
         <v>9</v>
       </c>
+      <c r="D5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1820,8 +1859,11 @@
       <c r="C6">
         <v>7</v>
       </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1831,8 +1873,11 @@
       <c r="C7">
         <v>6</v>
       </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1842,8 +1887,11 @@
       <c r="C8">
         <v>5</v>
       </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1853,8 +1901,11 @@
       <c r="C9">
         <v>4</v>
       </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1864,8 +1915,11 @@
       <c r="C10">
         <v>4</v>
       </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1875,8 +1929,11 @@
       <c r="C11">
         <v>4</v>
       </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1885,6 +1942,9 @@
       </c>
       <c r="C12">
         <v>4</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Multitask-stats.xlsx
+++ b/Multitask-stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yayax\projects\3body-simulator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Alexey_Pasechnik/projects/3body-simulator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BCA2F9-993D-416B-BAD2-AECCEBB78B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F192B877-9819-2C45-8A9E-5A98077B8AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="29920" windowHeight="17800" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>Macbook Pro Intel Core i7</t>
   </si>
@@ -50,13 +50,13 @@
     <t>Zenbook 14 UM3406GA</t>
   </si>
   <si>
-    <t>Aser Aspire</t>
+    <t>Workers</t>
   </si>
   <si>
-    <t>Time of 32 runs</t>
+    <t>Time of 2592 runs</t>
   </si>
   <si>
-    <t>Workers</t>
+    <t>1.0,1.0,0.0001,1,0.1,0,0,0,0,1,0.9,0-175-5,0-355-5,0,180,1000,100</t>
   </si>
 </sst>
 </file>
@@ -102,7 +102,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -120,7 +120,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -145,16 +145,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -176,7 +176,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 32 runs</c:v>
+                  <c:v>Time of 2592 runs</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Macbook Pro Intel Core i7</c:v>
@@ -185,9 +185,11 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -195,15 +197,17 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="6"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
+              <a:noFill/>
+              <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="70000"/>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -302,7 +306,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 32 runs</c:v>
+                  <c:v>Time of 2592 runs</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Macbook Apple M1 Pro</c:v>
@@ -311,9 +315,11 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -321,15 +327,17 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="6"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
+              <a:noFill/>
+              <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="70000"/>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -428,7 +436,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 32 runs</c:v>
+                  <c:v>Time of 2592 runs</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Zenbook 14 UM3406GA</c:v>
@@ -437,9 +445,11 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent3">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -447,15 +457,17 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="6"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
+              <a:noFill/>
+              <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
                 <a:solidFill>
-                  <a:schemeClr val="accent3"/>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="70000"/>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -554,18 +566,20 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 32 runs</c:v>
+                  <c:v>Time of 2592 runs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Aser Aspire</c:v>
+                  <c:v>Macbook Apple M1 Pro</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent4">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -573,15 +587,17 @@
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="6"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
+              <a:noFill/>
+              <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
                 <a:solidFill>
-                  <a:schemeClr val="accent4"/>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="70000"/>
+                  </a:schemeClr>
                 </a:solidFill>
+                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
@@ -631,6 +647,36 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -655,7 +701,9 @@
       <c:valAx>
         <c:axId val="990128272"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:max val="16"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -673,20 +721,28 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -717,6 +773,7 @@
       <c:valAx>
         <c:axId val="1331613056"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -735,20 +792,28 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -785,7 +850,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -900,7 +965,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="243">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -911,7 +976,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -927,21 +992,24 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -957,7 +1025,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -977,22 +1045,17 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -1001,37 +1064,49 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1041,22 +1116,26 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+            <a:alpha val="70000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -1086,15 +1165,13 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1104,7 +1181,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -1113,14 +1190,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1129,17 +1205,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -1148,14 +1224,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1167,21 +1243,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1200,7 +1270,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1219,17 +1289,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="50000"/>
             <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -1238,17 +1308,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -1269,7 +1338,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -1277,7 +1346,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1290,6 +1359,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1297,10 +1377,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -1315,17 +1395,17 @@
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
+    <cs:fontRef idx="major">
       <a:schemeClr val="tx1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="2000" kern="1200" spc="0" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
+      <cs:styleClr val="0"/>
     </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -1333,49 +1413,18 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="38100" cap="rnd" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
+  </cs:trendline>
+  <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -1385,32 +1434,48 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="0" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1419,16 +1484,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>127001</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>830384</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>78153</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1457,9 +1522,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1497,7 +1562,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -1603,7 +1668,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1773,17 +1838,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDD5B6A-F05D-A248-86D7-3519E8114CE9}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -1792,7 +1857,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>0</v>
@@ -1804,10 +1869,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1820,8 +1885,11 @@
       <c r="D3">
         <v>26</v>
       </c>
+      <c r="E3">
+        <v>269</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1834,8 +1902,11 @@
       <c r="D4">
         <v>16</v>
       </c>
+      <c r="E4">
+        <v>137</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1848,8 +1919,11 @@
       <c r="D5">
         <v>14</v>
       </c>
+      <c r="E5">
+        <v>93</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1862,8 +1936,11 @@
       <c r="D6">
         <v>11</v>
       </c>
+      <c r="E6">
+        <v>71</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1876,8 +1953,11 @@
       <c r="D7">
         <v>11</v>
       </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1890,8 +1970,11 @@
       <c r="D8">
         <v>10</v>
       </c>
+      <c r="E8">
+        <v>48</v>
+      </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1904,8 +1987,11 @@
       <c r="D9">
         <v>10</v>
       </c>
+      <c r="E9">
+        <v>41</v>
+      </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1918,8 +2004,11 @@
       <c r="D10">
         <v>10</v>
       </c>
+      <c r="E10">
+        <v>37</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1932,8 +2021,11 @@
       <c r="D11">
         <v>10</v>
       </c>
+      <c r="E11">
+        <v>36</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1945,6 +2037,14 @@
       </c>
       <c r="D12">
         <v>10</v>
+      </c>
+      <c r="E12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Multitask-stats.xlsx
+++ b/Multitask-stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Alexey_Pasechnik/projects/3body-simulator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yayax\projects\3body-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F192B877-9819-2C45-8A9E-5A98077B8AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3039383D-8340-480D-9C4A-83C702E4388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="29920" windowHeight="17800" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Macbook Pro Intel Core i7</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>1.0,1.0,0.0001,1,0.1,0,0,0,0,1,0.9,0-175-5,0-355-5,0,180,1000,100</t>
+  </si>
+  <si>
+    <t>Acer Aspire</t>
   </si>
 </sst>
 </file>
@@ -102,7 +105,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -120,7 +123,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -388,34 +391,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>25</c:v>
+                  <c:v>269</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -518,34 +521,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>26</c:v>
+                  <c:v>264</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16</c:v>
+                  <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -569,7 +572,7 @@
                   <c:v>Time of 2592 runs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Macbook Apple M1 Pro</c:v>
+                  <c:v>Acer Aspire</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -647,36 +650,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>269</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>137</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>93</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>71</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>57</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>48</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>35</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1522,9 +1495,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1562,7 +1535,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -1668,7 +1641,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1839,14 +1812,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDD5B6A-F05D-A248-86D7-3519E8114CE9}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="19.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1857,7 +1830,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>0</v>
@@ -1869,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1880,16 +1853,13 @@
         <v>58</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>269</v>
       </c>
       <c r="D3">
-        <v>26</v>
-      </c>
-      <c r="E3">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1897,16 +1867,13 @@
         <v>29</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="D4">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>137</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1914,16 +1881,13 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="D5">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>93</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1931,16 +1895,13 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1948,16 +1909,13 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1965,16 +1923,13 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="E8">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1982,16 +1937,13 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>41</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1999,16 +1951,13 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="E10">
-        <v>37</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2016,16 +1965,13 @@
         <v>17</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11">
-        <v>36</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2033,16 +1979,13 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>

--- a/Multitask-stats.xlsx
+++ b/Multitask-stats.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yayax\projects\3body-simulator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bitininkas/projects/3body-simulator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3039383D-8340-480D-9C4A-83C702E4388F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A2FC64-43E0-AD43-BF93-84BF3C282559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="26560" windowHeight="15920" xr2:uid="{362FF6B7-8D79-4B47-86DF-36CF33050B12}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Macbook Pro Intel Core i7</t>
   </si>
@@ -53,25 +53,102 @@
     <t>Workers</t>
   </si>
   <si>
-    <t>Time of 2592 runs</t>
-  </si>
-  <si>
-    <t>1.0,1.0,0.0001,1,0.1,0,0,0,0,1,0.9,0-175-5,0-355-5,0,180,1000,100</t>
-  </si>
-  <si>
-    <t>Acer Aspire</t>
+    <t>AWS Workspace</t>
+  </si>
+  <si>
+    <t>Acer Aspire V3-571G</t>
+  </si>
+  <si>
+    <t>M_1</t>
+  </si>
+  <si>
+    <t>M_2</t>
+  </si>
+  <si>
+    <t>M_3</t>
+  </si>
+  <si>
+    <t>a_in</t>
+  </si>
+  <si>
+    <t>e_in</t>
+  </si>
+  <si>
+    <t>i_in</t>
+  </si>
+  <si>
+    <t>Ω_in</t>
+  </si>
+  <si>
+    <t>ω_in</t>
+  </si>
+  <si>
+    <t>M_in</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>e_out</t>
+  </si>
+  <si>
+    <t>i_out</t>
+  </si>
+  <si>
+    <t>Ω_out</t>
+  </si>
+  <si>
+    <t>ω_out</t>
+  </si>
+  <si>
+    <t>M_out</t>
+  </si>
+  <si>
+    <t>T_max</t>
+  </si>
+  <si>
+    <t>Extra_time</t>
+  </si>
+  <si>
+    <t>Run configuration</t>
+  </si>
+  <si>
+    <t>Output points</t>
+  </si>
+  <si>
+    <t>0-175-5</t>
+  </si>
+  <si>
+    <t>0-355-5</t>
+  </si>
+  <si>
+    <t>Time of 2592 runs, secs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -95,17 +172,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -123,7 +204,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -179,7 +260,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 2592 runs</c:v>
+                  <c:v>Time of 2592 runs, secs</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Macbook Pro Intel Core i7</c:v>
@@ -261,34 +342,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>58</c:v>
+                  <c:v>608</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17</c:v>
+                  <c:v>127</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>122</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>17</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -309,7 +390,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 2592 runs</c:v>
+                  <c:v>Time of 2592 runs, secs</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Macbook Apple M1 Pro</c:v>
@@ -439,7 +520,7 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 2592 runs</c:v>
+                  <c:v>Time of 2592 runs, secs</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Zenbook 14 UM3406GA</c:v>
@@ -569,10 +650,10 @@
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Time of 2592 runs</c:v>
+                  <c:v>Time of 2592 runs, secs</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Acer Aspire</c:v>
+                  <c:v>Acer Aspire V3-571G</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -650,6 +731,36 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>557</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>472</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>476</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>479</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>477</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>474</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -657,6 +768,136 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-4073-2D4F-95DB-83811B5FC124}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1:$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Time of 2592 runs, secs</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>AWS Workspace</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                    <a:alpha val="70000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$3:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$3:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>596</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>317</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>248</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CF19-7B44-A2B6-AF5BAB209871}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -748,6 +989,8 @@
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
+          <c:max val="1200"/>
+          <c:min val="10"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1457,16 +1700,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>127001</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>44938</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>830384</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>78153</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>97692</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1495,9 +1738,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1535,7 +1778,7 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
@@ -1641,7 +1884,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1811,46 +2054,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDD5B6A-F05D-A248-86D7-3519E8114CE9}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>58</v>
+        <v>608</v>
       </c>
       <c r="C3">
         <v>269</v>
@@ -1858,13 +2106,19 @@
       <c r="D3">
         <v>264</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>1044</v>
+      </c>
+      <c r="F3">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>272</v>
       </c>
       <c r="C4">
         <v>137</v>
@@ -1872,13 +2126,19 @@
       <c r="D4">
         <v>159</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>557</v>
+      </c>
+      <c r="F4">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="C5">
         <v>93</v>
@@ -1886,13 +2146,19 @@
       <c r="D5">
         <v>121</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>510</v>
+      </c>
+      <c r="F5">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>71</v>
@@ -1900,13 +2166,19 @@
       <c r="D6">
         <v>97</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>472</v>
+      </c>
+      <c r="F6">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>57</v>
@@ -1914,13 +2186,19 @@
       <c r="D7">
         <v>88</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>476</v>
+      </c>
+      <c r="F7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="C8">
         <v>48</v>
@@ -1928,13 +2206,19 @@
       <c r="D8">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>475</v>
+      </c>
+      <c r="F8">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="C9">
         <v>41</v>
@@ -1942,13 +2226,19 @@
       <c r="D9">
         <v>75</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>470</v>
+      </c>
+      <c r="F9">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C10">
         <v>37</v>
@@ -1956,13 +2246,19 @@
       <c r="D10">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>479</v>
+      </c>
+      <c r="F10">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C11">
         <v>36</v>
@@ -1970,13 +2266,19 @@
       <c r="D11">
         <v>73</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>477</v>
+      </c>
+      <c r="F11">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C12">
         <v>35</v>
@@ -1984,15 +2286,167 @@
       <c r="D12">
         <v>73</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>5</v>
+      <c r="E12">
+        <v>474</v>
+      </c>
+      <c r="F12">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
